--- a/kname_webapp/data/hanja_dict.xlsx
+++ b/kname_webapp/data/hanja_dict.xlsx
@@ -4429,7 +4429,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>at peace</t>
+          <t>serene</t>
         </is>
       </c>
     </row>
@@ -15319,7 +15319,7 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>benevolent</t>
+          <t>to excel</t>
         </is>
       </c>
     </row>

--- a/kname_webapp/data/hanja_dict.xlsx
+++ b/kname_webapp/data/hanja_dict.xlsx
@@ -14967,7 +14967,7 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>daughter</t>
+          <t>luxuriant, flourishing</t>
         </is>
       </c>
     </row>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>a model</t>
+          <t>exemplary, a model</t>
         </is>
       </c>
     </row>

--- a/kname_webapp/data/hanja_dict.xlsx
+++ b/kname_webapp/data/hanja_dict.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>the universe</t>
+          <t>a home</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>a stone monument</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>moon</t>
+          <t>sweet</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>to enjoy</t>
+          <t>triumphant</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>noble rank</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>surroundings</t>
+          <t>vast, broad</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>merit</t>
+          <t>to nurture</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>bud</t>
+          <t>a cave</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>that</t>
+          <t>to accomplish</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>shadow</t>
+          <t>sunlight</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>graceful, feminine</t>
+          <t>graceful, lovely</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>metal</t>
+          <t>gold</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>to ripen</t>
+          <t>brilliant</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>to prevail</t>
+          <t>to knead</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>south</t>
+          <t>the warm south</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>graceful, feminine</t>
+          <t>graceful, lovely</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>stipend</t>
+          <t>good fortune</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>dignified</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>east</t>
+          <t>the rising east</t>
         </is>
       </c>
     </row>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>man</t>
+          <t>a youth</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>cool, clear</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>stipend</t>
+          <t>good fortune</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>night</t>
+          <t>a chestnut</t>
         </is>
       </c>
     </row>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>ten thousand</t>
+          <t>countless</t>
         </is>
       </c>
     </row>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>upright</t>
+          <t>to apply</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>law</t>
+          <t>a model, a pattern</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>things, substance</t>
+          <t>all things</t>
         </is>
       </c>
     </row>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>surname</t>
+          <t>a model, a pattern</t>
         </is>
       </c>
     </row>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>to receive</t>
+          <t>to revere, to offer</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>second</t>
+          <t>to assist</t>
         </is>
       </c>
     </row>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>a queen consort</t>
+          <t>royal</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>pearl</t>
+          <t>a pearl</t>
         </is>
       </c>
     </row>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>the first</t>
+          <t>a beginning</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>to scatter</t>
         </is>
       </c>
     </row>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>above</t>
+          <t>high, lofty</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>mutual</t>
+          <t>to assist</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>seal</t>
+          <t>a royal seal</t>
         </is>
       </c>
     </row>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>surname</t>
+          <t>a fortress</t>
         </is>
       </c>
     </row>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>pond</t>
+          <t>a pond</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>grandson</t>
+          <t>a descendant</t>
         </is>
       </c>
     </row>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>to print</t>
+          <t>to cleanse</t>
         </is>
       </c>
     </row>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>the first</t>
+          <t>a beginning</t>
         </is>
       </c>
     </row>
@@ -11931,7 +11931,7 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>truly</t>
+          <t>true, real</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>bride</t>
+          <t>a lineage</t>
         </is>
       </c>
     </row>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>clear, peaceful</t>
         </is>
       </c>
     </row>
@@ -12789,7 +12789,7 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>alike</t>
+          <t>gentle</t>
         </is>
       </c>
     </row>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>hundred million</t>
+          <t>at peace</t>
         </is>
       </c>
     </row>
@@ -13097,7 +13097,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>self</t>
+          <t>great</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>also, moreover</t>
+          <t>great</t>
         </is>
       </c>
     </row>
@@ -13537,7 +13537,7 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>to polish jade</t>
+          <t>fine jade</t>
         </is>
       </c>
     </row>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>a flowering hero</t>
+          <t>outstanding</t>
         </is>
       </c>
     </row>
@@ -14241,7 +14241,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>snail</t>
+          <t>a snail</t>
         </is>
       </c>
     </row>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>roof tile</t>
+          <t>a roof tile</t>
         </is>
       </c>
     </row>
@@ -14373,7 +14373,7 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>crosswise</t>
+          <t>to speak</t>
         </is>
       </c>
     </row>
@@ -14395,7 +14395,7 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>pond</t>
+          <t>vast, broad</t>
         </is>
       </c>
     </row>
@@ -14571,7 +14571,7 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>bathing</t>
+          <t>to cleanse</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>dragon</t>
+          <t>a dragon</t>
         </is>
       </c>
     </row>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>morning sun</t>
+          <t>the morning sun</t>
         </is>
       </c>
     </row>
@@ -14769,7 +14769,7 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>refined pattern</t>
+          <t>refined, cultured</t>
         </is>
       </c>
     </row>
@@ -14957,7 +14957,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>딸,고을이름</t>
+          <t>우거지다,고을이름</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -15209,7 +15209,7 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>moon</t>
+          <t>the moon</t>
         </is>
       </c>
     </row>
@@ -15517,7 +15517,7 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>hill</t>
+          <t>land</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>red gem</t>
+          <t>a red gem</t>
         </is>
       </c>
     </row>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>writing brush</t>
+          <t>a writing brush</t>
         </is>
       </c>
     </row>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>bird</t>
+          <t>a bird</t>
         </is>
       </c>
     </row>
@@ -15935,7 +15935,7 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>high mountain</t>
+          <t>a high mountain</t>
         </is>
       </c>
     </row>
@@ -16001,7 +16001,7 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>breast</t>
+          <t>to embrace</t>
         </is>
       </c>
     </row>
@@ -16045,7 +16045,7 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>righteous, just</t>
         </is>
       </c>
     </row>
@@ -16309,7 +16309,7 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>the next day</t>
+          <t>to help</t>
         </is>
       </c>
     </row>
@@ -16375,7 +16375,7 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>seal</t>
+          <t>a stamp</t>
         </is>
       </c>
     </row>
@@ -16573,7 +16573,7 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>to lift</t>
+          <t>to enter</t>
         </is>
       </c>
     </row>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>lotus seed</t>
+          <t>a peony</t>
         </is>
       </c>
     </row>
@@ -17123,7 +17123,7 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>weaving</t>
+          <t>an achievement</t>
         </is>
       </c>
     </row>
@@ -17453,7 +17453,7 @@
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>refined</t>
+          <t>settled, steady</t>
         </is>
       </c>
     </row>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>ridge</t>
+          <t>the origin</t>
         </is>
       </c>
     </row>
@@ -17959,7 +17959,7 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>all around</t>
+          <t>all-encompassing</t>
         </is>
       </c>
     </row>
@@ -19455,7 +19455,7 @@
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>wife</t>
+          <t>a spouse</t>
         </is>
       </c>
     </row>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>flesh</t>
+          <t>a place</t>
         </is>
       </c>
     </row>
@@ -19675,7 +19675,7 @@
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>moon</t>
+          <t>sweet</t>
         </is>
       </c>
     </row>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>keen of ear</t>
+          <t>wise, quick-witted</t>
         </is>
       </c>
     </row>
@@ -19983,7 +19983,7 @@
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>the most</t>
+          <t>utmost, supreme</t>
         </is>
       </c>
     </row>
@@ -20159,7 +20159,7 @@
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>day</t>
+          <t>to come forth</t>
         </is>
       </c>
     </row>
@@ -20291,7 +20291,7 @@
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>beside</t>
+          <t>a side</t>
         </is>
       </c>
     </row>
@@ -20511,7 +20511,7 @@
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>to be called</t>
+          <t>to praise</t>
         </is>
       </c>
     </row>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>a hexagram</t>
+          <t>decisive</t>
         </is>
       </c>
     </row>
@@ -21215,7 +21215,7 @@
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>melon seed</t>
+          <t>a petal</t>
         </is>
       </c>
     </row>
@@ -21369,7 +21369,7 @@
       </c>
       <c r="D952" t="inlineStr">
         <is>
-          <t>all around</t>
+          <t>widespread</t>
         </is>
       </c>
     </row>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="D961" t="inlineStr">
         <is>
-          <t>thing</t>
+          <t>quality, character</t>
         </is>
       </c>
     </row>
@@ -21589,7 +21589,7 @@
       </c>
       <c r="D962" t="inlineStr">
         <is>
-          <t>cord</t>
+          <t>to bestow</t>
         </is>
       </c>
     </row>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>sound of a carriage</t>
+          <t>to govern</t>
         </is>
       </c>
     </row>
@@ -21985,7 +21985,7 @@
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>to share</t>
+          <t>to divide</t>
         </is>
       </c>
     </row>
@@ -22249,7 +22249,7 @@
       </c>
       <c r="D992" t="inlineStr">
         <is>
-          <t>reed</t>
+          <t>to go</t>
         </is>
       </c>
     </row>
@@ -22425,7 +22425,7 @@
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>crimson</t>
+          <t>radiant, brilliant</t>
         </is>
       </c>
     </row>
@@ -23283,7 +23283,7 @@
       </c>
       <c r="D1039" t="inlineStr">
         <is>
-          <t>surname</t>
+          <t>surroundings</t>
         </is>
       </c>
     </row>
@@ -23591,7 +23591,7 @@
       </c>
       <c r="D1053" t="inlineStr">
         <is>
-          <t>crosswise</t>
+          <t>to span across</t>
         </is>
       </c>
     </row>
@@ -23767,7 +23767,7 @@
       </c>
       <c r="D1061" t="inlineStr">
         <is>
-          <t>a queen</t>
+          <t>a sovereign</t>
         </is>
       </c>
     </row>
@@ -24251,7 +24251,7 @@
       </c>
       <c r="D1083" t="inlineStr">
         <is>
-          <t>a name</t>
+          <t>a silk thread</t>
         </is>
       </c>
     </row>
@@ -24427,7 +24427,7 @@
       </c>
       <c r="D1091" t="inlineStr">
         <is>
-          <t>woman</t>
+          <t>beauty</t>
         </is>
       </c>
     </row>

--- a/kname_webapp/data/hanja_dict.xlsx
+++ b/kname_webapp/data/hanja_dict.xlsx
@@ -2823,7 +2823,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>even</t>
+          <t>balanced</t>
         </is>
       </c>
     </row>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>agreeable</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>great</t>
+          <t>fine jade, outstanding</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>taut, close</t>
+          <t>firm</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>greenery</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>virtue</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>sudden</t>
+          <t>to stand out</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>cool, clear</t>
+          <t>clear, calm</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>greenery</t>
         </is>
       </c>
     </row>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>countless</t>
+          <t>abundance</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>eldest</t>
+          <t>earnest</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>discreet, careful</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>white</t>
+          <t>pure, bright</t>
         </is>
       </c>
     </row>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>law</t>
+          <t>a model, a pattern</t>
         </is>
       </c>
     </row>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>high, lofty</t>
+          <t>lofty</t>
         </is>
       </c>
     </row>
@@ -12019,7 +12019,7 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>fresh</t>
         </is>
       </c>
     </row>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>far</t>
+          <t>far-reaching</t>
         </is>
       </c>
     </row>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>far</t>
+          <t>far-reaching, leisurely</t>
         </is>
       </c>
     </row>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>daylight</t>
+          <t>the sun</t>
         </is>
       </c>
     </row>
@@ -17629,7 +17629,7 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>even</t>
+          <t>balanced</t>
         </is>
       </c>
     </row>
@@ -21413,7 +21413,7 @@
       </c>
       <c r="D954" t="inlineStr">
         <is>
-          <t>even</t>
+          <t>peaceful, level</t>
         </is>
       </c>
     </row>
@@ -23305,7 +23305,7 @@
       </c>
       <c r="D1040" t="inlineStr">
         <is>
-          <t>certain</t>
+          <t>firm, sure</t>
         </is>
       </c>
     </row>
